--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/o-higgins.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1076575-1-CM26</t>
+          <t>544515-1-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.110.000-2</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE LA JUVENTUD</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>71502.32000000001</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>544515-1-CM26</t>
+          <t>544515-2-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,67 +874,6 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>51153.93</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>544515-2-CM26</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>72.240.400-9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
         <v>22149.61</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/o-higgins.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
